--- a/static/data/exports/Retro_UK_GE_2019.xlsx
+++ b/static/data/exports/Retro_UK_GE_2019.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>37</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>37</v>
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>37</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>37</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>37</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>37</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Q126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>37</v>
@@ -12931,20 +12931,20 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1487896</v>
+        <v>1487897</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Satyapal</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>16062</v>
+        <v>16061</v>
       </c>
       <c r="E202" t="n">
         <v>385</v>
@@ -12968,12 +12968,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Satyapal</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q202" t="b">
@@ -12993,20 +12993,20 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1487897</v>
+        <v>1487896</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Satyapal</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>16061</v>
+        <v>16062</v>
       </c>
       <c r="E203" t="n">
         <v>385</v>
@@ -13030,12 +13030,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Satyapal</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="Q203" t="b">
@@ -14233,11 +14233,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1487994</v>
+        <v>1487995</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Gopal Mani</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Gopal Mani</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14295,11 +14295,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1487995</v>
+        <v>1487994</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Gopal Mani</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Gopal Mani</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -17271,11 +17271,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1488326</v>
+        <v>1488325</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17333,11 +17333,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1488325</v>
+        <v>1488326</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22603,20 +22603,20 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1488801</v>
+        <v>1488802</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Furkan Ali Advocate</t>
+          <t>Lalit Kumar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>PSPL</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>16113</v>
+        <v>16162</v>
       </c>
       <c r="E358" t="n">
         <v>29</v>
@@ -22640,12 +22640,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Furkan Ali Advocate</t>
+          <t>Lalit Kumar</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>PSPL</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q358" t="b">
@@ -22665,20 +22665,20 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1488802</v>
+        <v>1488801</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Lalit Kumar</t>
+          <t>Furkan Ali Advocate</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>PSPL</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>16162</v>
+        <v>16113</v>
       </c>
       <c r="E359" t="n">
         <v>29</v>
@@ -22702,12 +22702,12 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Lalit Kumar</t>
+          <t>Furkan Ali Advocate</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>PSPL</t>
         </is>
       </c>
       <c r="Q359" t="b">
@@ -28121,20 +28121,20 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1489380</v>
+        <v>1489379</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Surendra Kumar Upadhayay</t>
+          <t>Dharmendra</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>UKKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>16063</v>
+        <v>16059</v>
       </c>
       <c r="E447" t="n">
         <v>44</v>
@@ -28158,12 +28158,12 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Surendra Kumar Upadhayay</t>
+          <t>Dharmendra</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>UKKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q447" t="b">
@@ -28183,20 +28183,20 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>1489379</v>
+        <v>1489380</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Dharmendra</t>
+          <t>Surendra Kumar Upadhayay</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UKKD</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>16059</v>
+        <v>16063</v>
       </c>
       <c r="E448" t="n">
         <v>44</v>
@@ -28220,12 +28220,12 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Dharmendra</t>
+          <t>Surendra Kumar Upadhayay</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UKKD</t>
         </is>
       </c>
       <c r="Q448" t="b">
@@ -31407,20 +31407,20 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1489671</v>
+        <v>1489672</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Narendra Chauhan</t>
+          <t>Reenu</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>BaSaPa</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>16112</v>
+        <v>16114</v>
       </c>
       <c r="E500" t="n">
         <v>50</v>
@@ -31444,12 +31444,12 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Narendra Chauhan</t>
+          <t>Reenu</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>BaSaPa</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="Q500" t="b">
@@ -31469,20 +31469,20 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>1489672</v>
+        <v>1489671</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Reenu</t>
+          <t>Narendra Chauhan</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>BaSaPa</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>16114</v>
+        <v>16112</v>
       </c>
       <c r="E501" t="n">
         <v>50</v>
@@ -31506,12 +31506,12 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Reenu</t>
+          <t>Narendra Chauhan</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>BaSaPa</t>
         </is>
       </c>
       <c r="Q501" t="b">
@@ -32693,7 +32693,7 @@
         </is>
       </c>
       <c r="Q520" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R520" t="n">
         <v>37</v>
@@ -33313,7 +33313,7 @@
         </is>
       </c>
       <c r="Q530" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R530" t="n">
         <v>37</v>
@@ -33933,7 +33933,7 @@
         </is>
       </c>
       <c r="Q540" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R540" t="n">
         <v>37</v>
@@ -34553,7 +34553,7 @@
         </is>
       </c>
       <c r="Q550" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R550" t="n">
         <v>37</v>
@@ -35173,7 +35173,7 @@
         </is>
       </c>
       <c r="Q560" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R560" t="n">
         <v>37</v>
@@ -35793,7 +35793,7 @@
         </is>
       </c>
       <c r="Q570" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R570" t="n">
         <v>37</v>
@@ -42489,7 +42489,7 @@
         </is>
       </c>
       <c r="Q678" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R678" t="n">
         <v>37</v>
@@ -42985,7 +42985,7 @@
         </is>
       </c>
       <c r="Q686" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R686" t="n">
         <v>37</v>
@@ -43481,7 +43481,7 @@
         </is>
       </c>
       <c r="Q694" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R694" t="n">
         <v>37</v>
@@ -43977,7 +43977,7 @@
         </is>
       </c>
       <c r="Q702" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R702" t="n">
         <v>37</v>
@@ -44473,7 +44473,7 @@
         </is>
       </c>
       <c r="Q710" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R710" t="n">
         <v>37</v>
@@ -44969,7 +44969,7 @@
         </is>
       </c>
       <c r="Q718" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R718" t="n">
         <v>37</v>
@@ -45589,7 +45589,7 @@
         </is>
       </c>
       <c r="Q728" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R728" t="n">
         <v>37</v>
@@ -46085,7 +46085,7 @@
         </is>
       </c>
       <c r="Q736" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R736" t="n">
         <v>37</v>
@@ -46581,7 +46581,7 @@
         </is>
       </c>
       <c r="Q744" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R744" t="n">
         <v>37</v>
@@ -47077,7 +47077,7 @@
         </is>
       </c>
       <c r="Q752" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R752" t="n">
         <v>37</v>
@@ -47341,20 +47341,20 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>1491584</v>
+        <v>1491585</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Er. Jyoti Prakash Tamta</t>
+          <t>Sukumar Vishvas</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D757" t="n">
-        <v>16098</v>
+        <v>16059</v>
       </c>
       <c r="E757" t="n">
         <v>224</v>
@@ -47378,12 +47378,12 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Er. Jyoti Prakash Tamta</t>
+          <t>Sukumar Vishvas</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q757" t="b">
@@ -47403,20 +47403,20 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>1491585</v>
+        <v>1491584</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Sukumar Vishvas</t>
+          <t>Er. Jyoti Prakash Tamta</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D758" t="n">
-        <v>16059</v>
+        <v>16098</v>
       </c>
       <c r="E758" t="n">
         <v>224</v>
@@ -47440,12 +47440,12 @@
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>Sukumar Vishvas</t>
+          <t>Er. Jyoti Prakash Tamta</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q758" t="b">
@@ -47573,7 +47573,7 @@
         </is>
       </c>
       <c r="Q760" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R760" t="n">
         <v>37</v>
@@ -48069,7 +48069,7 @@
         </is>
       </c>
       <c r="Q768" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R768" t="n">
         <v>37</v>
@@ -48565,7 +48565,7 @@
         </is>
       </c>
       <c r="Q776" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R776" t="n">
         <v>37</v>
@@ -49061,7 +49061,7 @@
         </is>
       </c>
       <c r="Q784" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R784" t="n">
         <v>37</v>
@@ -49557,7 +49557,7 @@
         </is>
       </c>
       <c r="Q792" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R792" t="n">
         <v>37</v>

--- a/static/data/exports/Retro_UK_GE_2019.xlsx
+++ b/static/data/exports/Retro_UK_GE_2019.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -14233,11 +14233,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1487995</v>
+        <v>1487994</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Gopal Mani</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Gopal Mani</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14295,11 +14295,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1487994</v>
+        <v>1487995</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Gopal Mani</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Gopal Mani</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -17271,11 +17271,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1488325</v>
+        <v>1488326</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Brij Bhushan Karanwal</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17333,11 +17333,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1488326</v>
+        <v>1488325</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Brij Bhushan Karanwal</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -28121,20 +28121,20 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1489379</v>
+        <v>1489380</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Dharmendra</t>
+          <t>Surendra Kumar Upadhayay</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UKKD</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>16059</v>
+        <v>16063</v>
       </c>
       <c r="E447" t="n">
         <v>44</v>
@@ -28158,12 +28158,12 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Dharmendra</t>
+          <t>Surendra Kumar Upadhayay</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UKKD</t>
         </is>
       </c>
       <c r="Q447" t="b">
@@ -28183,20 +28183,20 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>1489380</v>
+        <v>1489379</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Surendra Kumar Upadhayay</t>
+          <t>Dharmendra</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>UKKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>16063</v>
+        <v>16059</v>
       </c>
       <c r="E448" t="n">
         <v>44</v>
@@ -28220,12 +28220,12 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Surendra Kumar Upadhayay</t>
+          <t>Dharmendra</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>UKKD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q448" t="b">
@@ -47341,20 +47341,20 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>1491585</v>
+        <v>1491584</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Sukumar Vishvas</t>
+          <t>Er. Jyoti Prakash Tamta</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D757" t="n">
-        <v>16059</v>
+        <v>16098</v>
       </c>
       <c r="E757" t="n">
         <v>224</v>
@@ -47378,12 +47378,12 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Sukumar Vishvas</t>
+          <t>Er. Jyoti Prakash Tamta</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q757" t="b">
@@ -47403,20 +47403,20 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>1491584</v>
+        <v>1491585</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Er. Jyoti Prakash Tamta</t>
+          <t>Sukumar Vishvas</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D758" t="n">
-        <v>16098</v>
+        <v>16059</v>
       </c>
       <c r="E758" t="n">
         <v>224</v>
@@ -47440,12 +47440,12 @@
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>Er. Jyoti Prakash Tamta</t>
+          <t>Sukumar Vishvas</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q758" t="b">
